--- a/public/structure.xlsx
+++ b/public/structure.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nazarov.erbol\Desktop\ДАШБОРД\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2064558B-5A5E-4945-A6ED-0D2433AFE168}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7155C9E5-8473-4D0C-9CD5-BD6B42586383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="218">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="629" uniqueCount="217">
   <si>
     <t>Ф.И.О.</t>
   </si>
@@ -701,9 +701,6 @@
   </si>
   <si>
     <t>ДОВО</t>
-  </si>
-  <si>
-    <t>ДВОВО</t>
   </si>
   <si>
     <t>ЦУООЗ</t>
@@ -2803,8 +2800,8 @@
       <c r="A16" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>206</v>
+      <c r="B16" s="23" t="s">
+        <v>205</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>14</v>
@@ -7156,7 +7153,7 @@
         <v>160</v>
       </c>
       <c r="B29" s="14" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>14</v>
@@ -8188,7 +8185,7 @@
         <v>75</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>15</v>
@@ -8210,7 +8207,7 @@
         <v>81</v>
       </c>
       <c r="B31" s="36" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>15</v>
@@ -8232,7 +8229,7 @@
         <v>90</v>
       </c>
       <c r="B32" s="14" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C32" s="4" t="s">
         <v>14</v>
@@ -9266,7 +9263,7 @@
         <v>26</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>15</v>
@@ -9288,7 +9285,7 @@
         <v>27</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C34" s="2" t="s">
         <v>15</v>
@@ -9310,7 +9307,7 @@
         <v>29</v>
       </c>
       <c r="B35" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C35" s="24" t="s">
         <v>17</v>
@@ -9334,7 +9331,7 @@
         <v>30</v>
       </c>
       <c r="B36" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>14</v>
@@ -9358,7 +9355,7 @@
         <v>107</v>
       </c>
       <c r="B37" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>108</v>
@@ -9382,7 +9379,7 @@
         <v>31</v>
       </c>
       <c r="B38" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C38" s="11" t="s">
         <v>14</v>
@@ -10416,7 +10413,7 @@
         <v>32</v>
       </c>
       <c r="B39" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>15</v>
@@ -10440,7 +10437,7 @@
         <v>33</v>
       </c>
       <c r="B40" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C40" s="11" t="s">
         <v>14</v>
@@ -11474,7 +11471,7 @@
         <v>34</v>
       </c>
       <c r="B41" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>108</v>
@@ -11498,7 +11495,7 @@
         <v>35</v>
       </c>
       <c r="B42" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C42" s="11" t="s">
         <v>14</v>
@@ -12532,7 +12529,7 @@
         <v>36</v>
       </c>
       <c r="B43" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>15</v>
@@ -12556,7 +12553,7 @@
         <v>106</v>
       </c>
       <c r="B44" s="23" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>15</v>
@@ -12577,10 +12574,10 @@
     </row>
     <row r="45" spans="1:1018" ht="31.5" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A45" s="46" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B45" s="46" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C45" s="20" t="s">
         <v>17</v>
@@ -12602,7 +12599,7 @@
         <v>101</v>
       </c>
       <c r="B46" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C46" s="28" t="s">
         <v>37</v>
@@ -12624,7 +12621,7 @@
         <v>102</v>
       </c>
       <c r="B47" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C47" s="40" t="s">
         <v>14</v>
@@ -12646,7 +12643,7 @@
         <v>120</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C48" s="40" t="s">
         <v>15</v>
@@ -12668,7 +12665,7 @@
         <v>78</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C49" s="40" t="s">
         <v>39</v>
@@ -12690,7 +12687,7 @@
         <v>79</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>65</v>
@@ -12712,7 +12709,7 @@
         <v>76</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>77</v>
@@ -12734,7 +12731,7 @@
         <v>121</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>122</v>
@@ -12756,7 +12753,7 @@
         <v>110</v>
       </c>
       <c r="B53" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>111</v>
@@ -12778,7 +12775,7 @@
         <v>109</v>
       </c>
       <c r="B54" s="13" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>88</v>
@@ -12800,7 +12797,7 @@
         <v>86</v>
       </c>
       <c r="B55" s="14" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C55" s="24" t="s">
         <v>17</v>
@@ -13834,7 +13831,7 @@
         <v>89</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>15</v>
@@ -13858,7 +13855,7 @@
         <v>40</v>
       </c>
       <c r="B57" s="43" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C57" s="2" t="s">
         <v>14</v>
@@ -13882,7 +13879,7 @@
         <v>41</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>15</v>
@@ -13906,7 +13903,7 @@
         <v>42</v>
       </c>
       <c r="B59" s="13" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C59" s="30" t="s">
         <v>15</v>
@@ -13930,7 +13927,7 @@
         <v>80</v>
       </c>
       <c r="B60" s="42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C60" s="28" t="s">
         <v>14</v>
@@ -13954,7 +13951,7 @@
         <v>118</v>
       </c>
       <c r="B61" s="42" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C61" s="28" t="s">
         <v>119</v>
@@ -13978,7 +13975,7 @@
         <v>43</v>
       </c>
       <c r="B62" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>17</v>
@@ -14002,7 +13999,7 @@
         <v>44</v>
       </c>
       <c r="B63" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C63" s="4" t="s">
         <v>14</v>
@@ -15036,7 +15033,7 @@
         <v>45</v>
       </c>
       <c r="B64" s="43" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>15</v>
@@ -15060,7 +15057,7 @@
         <v>46</v>
       </c>
       <c r="B65" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C65" s="4" t="s">
         <v>14</v>
@@ -16094,7 +16091,7 @@
         <v>47</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>15</v>
@@ -16118,7 +16115,7 @@
         <v>112</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>15</v>
@@ -16142,7 +16139,7 @@
         <v>48</v>
       </c>
       <c r="B68" s="26" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C68" s="4" t="s">
         <v>127</v>
@@ -17176,7 +17173,7 @@
         <v>49</v>
       </c>
       <c r="B69" s="11" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C69" s="4" t="s">
         <v>126</v>
@@ -18210,7 +18207,7 @@
         <v>50</v>
       </c>
       <c r="B70" s="12" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C70" s="1" t="s">
         <v>51</v>
@@ -18234,7 +18231,7 @@
         <v>52</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>14</v>
@@ -18258,7 +18255,7 @@
         <v>82</v>
       </c>
       <c r="B72" s="36" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>15</v>
@@ -18282,7 +18279,7 @@
         <v>53</v>
       </c>
       <c r="B73" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>15</v>
@@ -18306,7 +18303,7 @@
         <v>104</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>14</v>
@@ -18330,7 +18327,7 @@
         <v>83</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>39</v>
@@ -18354,7 +18351,7 @@
         <v>84</v>
       </c>
       <c r="B76" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>15</v>
@@ -18378,7 +18375,7 @@
         <v>54</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>15</v>
@@ -18402,7 +18399,7 @@
         <v>105</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>15</v>
@@ -18426,7 +18423,7 @@
         <v>55</v>
       </c>
       <c r="B79" s="19" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>17</v>
@@ -18450,7 +18447,7 @@
         <v>56</v>
       </c>
       <c r="B80" s="15" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C80" s="4" t="s">
         <v>10</v>
@@ -19484,7 +19481,7 @@
         <v>57</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C81" s="2" t="s">
         <v>39</v>
@@ -19508,7 +19505,7 @@
         <v>58</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>39</v>
@@ -19532,7 +19529,7 @@
         <v>59</v>
       </c>
       <c r="B83" s="11" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C83" s="4" t="s">
         <v>60</v>
@@ -20566,7 +20563,7 @@
         <v>61</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>39</v>
@@ -20590,7 +20587,7 @@
         <v>62</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C85" s="2" t="s">
         <v>128</v>
@@ -20614,7 +20611,7 @@
         <v>123</v>
       </c>
       <c r="B86" s="45" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>114</v>
@@ -20639,7 +20636,7 @@
         <v>125</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>14</v>
@@ -20663,7 +20660,7 @@
     <row r="88" spans="1:1018" s="8" customFormat="1" ht="47.25" outlineLevel="1" x14ac:dyDescent="0.25">
       <c r="A88" s="11"/>
       <c r="B88" s="11" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C88" s="11" t="s">
         <v>63</v>
@@ -21693,7 +21690,7 @@
         <v>148</v>
       </c>
       <c r="B89" s="11" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C89" s="11" t="s">
         <v>64</v>
